--- a/docs/StructureDefinition-space-emergency-condition.xlsx
+++ b/docs/StructureDefinition-space-emergency-condition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-space-emergency-condition.xlsx
+++ b/docs/StructureDefinition-space-emergency-condition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="359">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/space-emergency-condition</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/space-emergency-condition</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -464,7 +467,7 @@
     <t>missionContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/mission-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mission-context}
 </t>
   </si>
   <si>
@@ -484,7 +487,7 @@
     <t>missionPhase</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://mitre.org/fhir/space-health/StructureDefinition/mission-phase}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mission-phase}
 </t>
   </si>
   <si>
@@ -702,7 +705,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/ValueSet/space-emergency-type-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/space-emergency-type-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -769,7 +772,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://mitre.org/fhir/space-health/StructureDefinition/Astronaut)
+    <t xml:space="preserve">Reference(https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/astronaut)
 </t>
   </si>
   <si>
@@ -1403,54 +1406,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1473,7 +1478,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="66.578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="81.42578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1488,7 +1493,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="71.6640625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.16796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="72.15625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>
@@ -1508,138 +1513,138 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1647,10 +1652,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1662,13 +1667,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1719,31 +1724,31 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>20</v>
@@ -1754,10 +1759,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1765,10 +1770,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1777,19 +1782,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1839,13 +1844,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1874,10 +1879,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1885,10 +1890,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1897,16 +1902,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1957,19 +1962,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -1992,10 +1997,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2003,31 +2008,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2077,19 +2082,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2112,10 +2117,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2123,10 +2128,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2138,16 +2143,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2173,13 +2178,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2197,19 +2202,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2232,21 +2237,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2258,16 +2263,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2317,19 +2322,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2341,7 +2346,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>20</v>
@@ -2352,21 +2357,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2378,16 +2383,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2437,13 +2442,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2461,7 +2466,7 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>20</v>
@@ -2472,10 +2477,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2483,10 +2488,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2498,13 +2503,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2543,29 +2548,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2588,26 +2593,26 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -2616,13 +2621,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2673,19 +2678,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2708,26 +2713,26 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>20</v>
@@ -2736,13 +2741,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2793,19 +2798,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -2828,45 +2833,45 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -2915,19 +2920,19 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -2939,7 +2944,7 @@
         <v>20</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>20</v>
@@ -2950,10 +2955,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2961,10 +2966,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2973,22 +2978,22 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -3037,22 +3042,22 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>20</v>
@@ -3061,10 +3066,10 @@
         <v>20</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>20</v>
@@ -3072,10 +3077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3083,31 +3088,31 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3133,13 +3138,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3157,34 +3162,34 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>20</v>
@@ -3192,10 +3197,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3203,31 +3208,31 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3253,13 +3258,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3277,45 +3282,45 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AG15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>182</v>
-      </c>
       <c r="AP15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3323,10 +3328,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3338,16 +3343,16 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3373,13 +3378,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3397,34 +3402,34 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>20</v>
@@ -3432,10 +3437,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3443,13 +3448,13 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>20</v>
@@ -3458,16 +3463,16 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3493,13 +3498,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3517,78 +3522,78 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3613,11 +3618,11 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -3635,45 +3640,45 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3681,10 +3686,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3693,19 +3698,19 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3731,13 +3736,13 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -3755,78 +3760,78 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -3875,34 +3880,34 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>20</v>
@@ -3910,10 +3915,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3921,10 +3926,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3933,19 +3938,19 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3995,34 +4000,34 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>20</v>
@@ -4030,10 +4035,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4041,31 +4046,31 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4115,34 +4120,34 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>20</v>
@@ -4150,10 +4155,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4161,10 +4166,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4176,16 +4181,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4235,19 +4240,19 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
@@ -4259,10 +4264,10 @@
         <v>20</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>20</v>
@@ -4270,10 +4275,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4281,10 +4286,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4293,16 +4298,16 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4353,19 +4358,19 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -4374,13 +4379,13 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>20</v>
@@ -4388,10 +4393,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4399,10 +4404,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4411,16 +4416,16 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4471,19 +4476,19 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -4495,10 +4500,10 @@
         <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>20</v>
@@ -4506,10 +4511,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4517,10 +4522,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4529,16 +4534,16 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4589,19 +4594,19 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
@@ -4610,13 +4615,13 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>20</v>
@@ -4624,10 +4629,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4635,10 +4640,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4650,13 +4655,13 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4707,19 +4712,19 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
@@ -4731,7 +4736,7 @@
         <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -4742,10 +4747,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4753,10 +4758,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4768,13 +4773,13 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4825,13 +4830,13 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
@@ -4849,7 +4854,7 @@
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -4860,21 +4865,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -4886,16 +4891,16 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4945,19 +4950,19 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
@@ -4969,7 +4974,7 @@
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -4980,45 +4985,45 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5067,19 +5072,19 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -5091,7 +5096,7 @@
         <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -5102,10 +5107,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5113,10 +5118,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5128,13 +5133,13 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5161,13 +5166,13 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5185,31 +5190,31 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -5220,10 +5225,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5231,10 +5236,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5246,13 +5251,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5303,19 +5308,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5327,7 +5332,7 @@
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -5338,10 +5343,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5349,10 +5354,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5364,13 +5369,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5397,13 +5402,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5421,19 +5426,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -5445,7 +5450,7 @@
         <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -5456,10 +5461,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5467,10 +5472,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5482,16 +5487,16 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5541,19 +5546,19 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
@@ -5565,7 +5570,7 @@
         <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -5576,10 +5581,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5587,10 +5592,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5602,13 +5607,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5659,13 +5664,13 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
@@ -5683,7 +5688,7 @@
         <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -5694,21 +5699,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5720,16 +5725,16 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5779,19 +5784,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -5803,7 +5808,7 @@
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -5814,45 +5819,45 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5901,19 +5906,19 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
@@ -5925,7 +5930,7 @@
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -5936,10 +5941,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5947,10 +5952,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -5959,16 +5964,16 @@
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5995,13 +6000,13 @@
         <v>20</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>20</v>
@@ -6019,34 +6024,34 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>20</v>
@@ -6054,10 +6059,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6065,10 +6070,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6077,16 +6082,16 @@
         <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6137,34 +6142,34 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>20</v>
@@ -6172,10 +6177,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6183,13 +6188,13 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>20</v>
@@ -6198,13 +6203,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6255,31 +6260,31 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
